--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_first_charge.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_first_charge.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21585" windowHeight="8070"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_recharge" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
   <si>
     <t>唯一id</t>
   </si>
@@ -936,11 +937,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1272,6 +1273,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="13.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" style="1" customWidth="1"/>
+    <col min="8" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="11.125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="189" customHeight="1" spans="1:15">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:15">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:15">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="F10" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="F11" s="9"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="F12" s="9"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G3:H3">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A349:B349">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A350:B350">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A351:B351">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A416:B416">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I4">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9:J11">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:B324 A336:B348 A352:B406 A410:B415">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10:H12">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A325:B335">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A407:B409">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -1472,7 +1743,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="4">
         <v>301</v>
       </c>
@@ -1501,7 +1772,7 @@
       <c r="L5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="8" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="1" t="s">
@@ -1511,7 +1782,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="4">
         <v>302</v>
       </c>
@@ -1538,14 +1809,14 @@
       <c r="L6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" s="1" customFormat="1" spans="1:15">
       <c r="A7" s="4">
         <v>303</v>
       </c>
@@ -1572,14 +1843,14 @@
       <c r="L7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="8" t="s">
         <v>67</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" s="1" customFormat="1" spans="1:15">
       <c r="A8" s="4">
         <v>304</v>
       </c>
@@ -1603,7 +1874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" s="1" customFormat="1" spans="1:15">
       <c r="A9" s="4">
         <v>305</v>
       </c>
@@ -1627,7 +1898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" s="1" customFormat="1" spans="1:15">
       <c r="A10" s="4">
         <v>306</v>
       </c>
@@ -1650,69 +1921,68 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="10:10">
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="6:10">
-      <c r="F16" s="8"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="6:10">
-      <c r="F17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="6:6">
-      <c r="F18" s="8"/>
+    <row r="15" s="1" customFormat="1" spans="1:15">
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:15">
+      <c r="F16" s="9"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="6:10">
+      <c r="F17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="6:10">
+      <c r="F18" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G3:H3">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A355:B355">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A356:B356">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A357:B357">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A422:B422">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I4">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15:J17">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B9">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:B330 A342:B354 A358:B412 A416:B421">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:H18">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A331:B341">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A413:B415">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:B330 A342:B354 A358:B412 A416:B421">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:H18">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A331:B341">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A413:B415">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>